--- a/reports/Debug-purgatory-20260111/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260111/Week Total (Prior Year)_Visits.xlsx
@@ -588,10 +588,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="C15" s="2">
         <v>9</v>
@@ -630,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>995</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -647,7 +647,7 @@
         <v>45666</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>832</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>45667</v>
       </c>
       <c r="C18" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -675,7 +675,7 @@
         <v>45667</v>
       </c>
       <c r="C19" s="2">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="C20" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -703,10 +703,10 @@
         <v>45668</v>
       </c>
       <c r="C21" s="2">
-        <v>5</v>
+        <v>988</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45669</v>
+        <v>45668</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -731,7 +731,7 @@
         <v>45669</v>
       </c>
       <c r="C23" s="2">
-        <v>126</v>
+        <v>1847</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -955,10 +955,10 @@
         <v>45663</v>
       </c>
       <c r="C39" s="2">
-        <v>1071</v>
+        <v>4</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,10 +966,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C40" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -980,10 +980,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C41" s="2">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -997,10 +997,10 @@
         <v>45664</v>
       </c>
       <c r="C42" s="2">
-        <v>219</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1008,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45664</v>
+        <v>45666</v>
       </c>
       <c r="C43" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45665</v>
+        <v>45667</v>
       </c>
       <c r="C44" s="2">
-        <v>1322</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45665</v>
+        <v>45667</v>
       </c>
       <c r="C45" s="2">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="C46" s="2">
-        <v>828</v>
+        <v>15</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45666</v>
+        <v>45668</v>
       </c>
       <c r="C47" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>45666</v>
+        <v>45669</v>
       </c>
       <c r="C48" s="2">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>45667</v>
+        <v>45669</v>
       </c>
       <c r="C49" s="2">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,10 +1106,10 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45668</v>
+        <v>45664</v>
       </c>
       <c r="C50" s="2">
-        <v>2250</v>
+        <v>751</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>45669</v>
+        <v>45664</v>
       </c>
       <c r="C51" s="2">
-        <v>563</v>
+        <v>87</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,10 +1134,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>45669</v>
+        <v>45666</v>
       </c>
       <c r="C52" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45669</v>
+        <v>45667</v>
       </c>
       <c r="C53" s="2">
-        <v>80</v>
+        <v>1406</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C54" s="2">
-        <v>3</v>
+        <v>869</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,10 +1176,10 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C55" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>5</v>
@@ -1190,10 +1190,10 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>45665</v>
+        <v>45667</v>
       </c>
       <c r="C56" s="2">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1204,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C57" s="2">
-        <v>995</v>
+        <v>14</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,13 +1218,13 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45666</v>
+        <v>45663</v>
       </c>
       <c r="C58" s="2">
-        <v>832</v>
+        <v>238</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C59" s="2">
-        <v>10</v>
+        <v>899</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="C60" s="2">
-        <v>4</v>
+        <v>132</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1260,10 +1260,10 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45668</v>
+        <v>45665</v>
       </c>
       <c r="C61" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>5</v>
@@ -1274,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45668</v>
+        <v>45665</v>
       </c>
       <c r="C62" s="2">
-        <v>988</v>
+        <v>3</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1288,13 +1288,13 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C63" s="2">
-        <v>36</v>
+        <v>236</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,13 +1302,13 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>45669</v>
+        <v>45666</v>
       </c>
       <c r="C64" s="2">
-        <v>1847</v>
+        <v>4</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,10 +1316,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C65" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C66" s="2">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45665</v>
+        <v>45669</v>
       </c>
       <c r="C67" s="2">
-        <v>226</v>
+        <v>173</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
@@ -1358,13 +1358,13 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C68" s="2">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1375,7 +1375,7 @@
         <v>45665</v>
       </c>
       <c r="C69" s="2">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>5</v>
@@ -1386,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C70" s="2">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,13 +1400,13 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>45668</v>
+        <v>45665</v>
       </c>
       <c r="C71" s="2">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1414,13 +1414,13 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>45668</v>
+        <v>45665</v>
       </c>
       <c r="C72" s="2">
-        <v>268</v>
+        <v>115</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C73" s="2">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1442,13 +1442,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>45669</v>
+        <v>45668</v>
       </c>
       <c r="C74" s="2">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>45664</v>
+        <v>45668</v>
       </c>
       <c r="C75" s="2">
-        <v>751</v>
+        <v>268</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45664</v>
+        <v>45668</v>
       </c>
       <c r="C76" s="2">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1484,13 +1484,13 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>45666</v>
+        <v>45669</v>
       </c>
       <c r="C77" s="2">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,13 +1498,13 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C78" s="2">
-        <v>1406</v>
+        <v>1071</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1512,13 +1512,13 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C79" s="2">
-        <v>869</v>
+        <v>3</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1526,10 +1526,10 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45667</v>
+        <v>45663</v>
       </c>
       <c r="C80" s="2">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>5</v>
@@ -1540,13 +1540,13 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="C81" s="2">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1554,13 +1554,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45669</v>
+        <v>45664</v>
       </c>
       <c r="C82" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1568,13 +1568,13 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45663</v>
+        <v>45665</v>
       </c>
       <c r="C83" s="2">
-        <v>238</v>
+        <v>1322</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1582,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45663</v>
+        <v>45665</v>
       </c>
       <c r="C84" s="2">
-        <v>899</v>
+        <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>45664</v>
+        <v>45666</v>
       </c>
       <c r="C85" s="2">
-        <v>132</v>
+        <v>828</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,10 +1610,10 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="C86" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>5</v>
@@ -1624,10 +1624,10 @@
         <v>1</v>
       </c>
       <c r="B87" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="C87" s="2">
-        <v>3</v>
+        <v>133</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1638,13 +1638,13 @@
         <v>1</v>
       </c>
       <c r="B88" s="2">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="C88" s="2">
-        <v>236</v>
+        <v>8</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1652,13 +1652,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45666</v>
+        <v>45668</v>
       </c>
       <c r="C89" s="2">
-        <v>4</v>
+        <v>2250</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,13 +1666,13 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>45667</v>
+        <v>45669</v>
       </c>
       <c r="C90" s="2">
-        <v>125</v>
+        <v>563</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1683,7 +1683,7 @@
         <v>45669</v>
       </c>
       <c r="C91" s="2">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1697,10 +1697,10 @@
         <v>45669</v>
       </c>
       <c r="C92" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
